--- a/Cyber_Journey_IAM_Access_Review.xlsx
+++ b/Cyber_Journey_IAM_Access_Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B39A7A420137BE1C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{13F2B1AD-D2D8-4CFC-9F9F-8F16496A1789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27E0025E-FB17-435A-840A-3067A53A8B49}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{13F2B1AD-D2D8-4CFC-9F9F-8F16496A1789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6026045B-4D94-489E-A8DD-5033725F340C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2124AFF3-5773-47DD-BDDA-2B0E9C4A1F65}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2124AFF3-5773-47DD-BDDA-2B0E9C4A1F65}"/>
   </bookViews>
   <sheets>
     <sheet name="Departments &amp; Roles" sheetId="1" r:id="rId1"/>
@@ -197,9 +197,6 @@
     <t>SIEM, Entra ID, VPN, Finance App</t>
   </si>
   <si>
-    <t>What you've built so far</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">What access do employees </t>
     </r>
@@ -261,9 +258,6 @@
     <t>Reason</t>
   </si>
   <si>
-    <t>Ask yourself three questions:</t>
-  </si>
-  <si>
     <t>Does Sarah have everything required for her role?</t>
   </si>
   <si>
@@ -421,6 +415,12 @@
   </si>
   <si>
     <t>Current access matches the authorized access defined for Sales Representative role.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the Departments, Roles, and Authorized Systems that the employees of Northstar are in. </t>
+  </si>
+  <si>
+    <t>Ask these three questions:</t>
   </si>
 </sst>
 </file>
@@ -478,9 +478,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,6 +497,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -892,12 +897,12 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G13" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="G14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +915,7 @@
   <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
@@ -918,20 +923,20 @@
     <col min="9" max="9" width="37.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
+    <row r="3" spans="2:9" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1076,7 +1081,7 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -1107,7 +1112,7 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="I15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1135,33 +1140,33 @@
     <col min="14" max="14" width="73.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C3" t="s">
+    <row r="3" spans="3:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="K3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.35">
@@ -1184,13 +1189,13 @@
         <v>32</v>
       </c>
       <c r="I4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" t="s">
         <v>65</v>
       </c>
-      <c r="J4" t="s">
-        <v>67</v>
-      </c>
       <c r="K4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.35">
@@ -1213,13 +1218,13 @@
         <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.35">
@@ -1230,7 +1235,7 @@
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -1242,13 +1247,13 @@
         <v>37</v>
       </c>
       <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
         <v>65</v>
       </c>
-      <c r="J6" t="s">
-        <v>67</v>
-      </c>
       <c r="K6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.35">
@@ -1271,13 +1276,13 @@
         <v>13</v>
       </c>
       <c r="I7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" t="s">
         <v>65</v>
       </c>
-      <c r="J7" t="s">
-        <v>67</v>
-      </c>
       <c r="K7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.35">
@@ -1285,7 +1290,7 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>2</v>
@@ -1300,13 +1305,13 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" t="s">
         <v>65</v>
       </c>
-      <c r="J8" t="s">
-        <v>67</v>
-      </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.35">
@@ -1329,13 +1334,13 @@
         <v>42</v>
       </c>
       <c r="I9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s">
         <v>65</v>
       </c>
-      <c r="J9" t="s">
-        <v>67</v>
-      </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.35">
@@ -1346,7 +1351,7 @@
         <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -1358,13 +1363,13 @@
         <v>44</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.35">
@@ -1387,13 +1392,13 @@
         <v>46</v>
       </c>
       <c r="I11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="3:11" x14ac:dyDescent="0.35">
@@ -1401,7 +1406,7 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
         <v>4</v>
@@ -1416,13 +1421,13 @@
         <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.35">
@@ -1445,53 +1450,53 @@
         <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N27" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="14:14" x14ac:dyDescent="0.35">
       <c r="N30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1514,24 +1519,24 @@
     <col min="9" max="9" width="52.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C3" t="s">
+    <row r="3" spans="3:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="G3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.35">
@@ -1542,16 +1547,16 @@
         <v>33</v>
       </c>
       <c r="E4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" t="s">
         <v>89</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>90</v>
-      </c>
-      <c r="G4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.35">
@@ -1562,16 +1567,16 @@
         <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s">
         <v>93</v>
-      </c>
-      <c r="G5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.35">
@@ -1582,16 +1587,16 @@
         <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" t="s">
         <v>96</v>
-      </c>
-      <c r="G6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H6" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.35">
@@ -1599,19 +1604,19 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" t="s">
         <v>99</v>
       </c>
-      <c r="F7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" t="s">
-        <v>101</v>
-      </c>
       <c r="H7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.35">
@@ -1619,24 +1624,24 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" t="s">
         <v>89</v>
       </c>
-      <c r="F8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" t="s">
-        <v>91</v>
-      </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="9:9" x14ac:dyDescent="0.35">
       <c r="I19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
